--- a/Modules/kNOT/kNOT_BOM.xlsx
+++ b/Modules/kNOT/kNOT_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My-Dev\Modular Synth\Avalon Harmonics\kNOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E71B06A-DF95-42C3-8BAE-1BF37DA34764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2EC49D-A00D-4833-ABEE-6A4FFC6E4844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -164,15 +164,9 @@
     <t>Pushernut</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/black-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Gold</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/pushernuts-gold-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Male Header 2.54mm</t>
   </si>
   <si>
@@ -305,9 +299,6 @@
     <t>https://www.tme.eu/de/en/details/zl201-40g/pin-headers/connfly/ds1021-1-40sf11-b/</t>
   </si>
   <si>
-    <t>https://www.tme.eu/de/en/details/zl202-80g/pin-headers/connfly/ds1021-2-40sf11/</t>
-  </si>
-  <si>
     <t>https://www.buerklin.com/en/p/quadrios/wirewound-resistors/22p046/73P0034/</t>
   </si>
   <si>
@@ -708,6 +699,15 @@
   </si>
   <si>
     <t>Parts  with underline are on the front PCB!</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57164621578504</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57166910816520</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/de/en/details/zl202-10g/pin-headers/connfly/ds1021-2-5sf11-b/</t>
   </si>
 </sst>
 </file>
@@ -1601,7 +1601,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="G2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -1636,16 +1636,16 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
         <v>24</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>37</v>
@@ -1659,16 +1659,16 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
         <v>24</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>37</v>
@@ -1682,16 +1682,16 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
         <v>24</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>37</v>
@@ -1705,16 +1705,16 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>37</v>
@@ -1728,19 +1728,19 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" t="s">
         <v>75</v>
       </c>
-      <c r="D7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" t="s">
-        <v>77</v>
-      </c>
       <c r="F7" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1751,19 +1751,19 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
         <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J8" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -1777,16 +1777,16 @@
         <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E9" t="s">
         <v>25</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1800,16 +1800,16 @@
         <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
         <v>26</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J10" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -1823,13 +1823,13 @@
         <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
         <v>35</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>38</v>
@@ -1852,10 +1852,10 @@
         <v>20</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -1863,7 +1863,7 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
@@ -1872,13 +1872,13 @@
         <v>31</v>
       </c>
       <c r="E13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1898,10 +1898,10 @@
         <v>29</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J14" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -1915,16 +1915,16 @@
         <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J15" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -1932,13 +1932,13 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
         <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E16" t="s">
         <v>28</v>
@@ -1947,7 +1947,7 @@
         <v>40</v>
       </c>
       <c r="J16" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -1955,22 +1955,22 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E17" t="s">
         <v>27</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J17" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -1978,22 +1978,22 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E18" t="s">
         <v>27</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J18" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -2001,22 +2001,22 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E19" t="s">
         <v>27</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -2024,22 +2024,22 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E20" t="s">
         <v>27</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
@@ -2059,10 +2059,10 @@
         <v>27</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="J21" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -2070,19 +2070,19 @@
         <v>1</v>
       </c>
       <c r="B23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23" t="s">
         <v>50</v>
       </c>
-      <c r="C23" t="s">
+      <c r="F23" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E23" t="s">
-        <v>52</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="J23" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -2090,19 +2090,19 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" t="s">
         <v>54</v>
       </c>
-      <c r="C24" t="s">
+      <c r="F24" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E24" t="s">
-        <v>56</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="J24" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -2110,19 +2110,19 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" t="s">
         <v>58</v>
       </c>
-      <c r="C25" t="s">
+      <c r="F25" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E25" t="s">
-        <v>60</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="J25" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -2136,13 +2136,13 @@
         <v>42</v>
       </c>
       <c r="E27" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="J27" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -2150,19 +2150,19 @@
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28" t="s">
         <v>42</v>
       </c>
       <c r="E28" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="J28" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -2170,7 +2170,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B30" s="5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -2191,25 +2191,25 @@
     <hyperlink ref="F14" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
     <hyperlink ref="F15" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
     <hyperlink ref="F16" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="F27" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="F28" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="J20" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="J19" r:id="rId17" xr:uid="{3EC0FADE-B5DB-495B-A25A-8E9C82905237}"/>
-    <hyperlink ref="F13" r:id="rId18" xr:uid="{0D186728-B786-4B2E-9671-D0877C50C69C}"/>
-    <hyperlink ref="F25" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="F24" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="F23" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="F17:F18" r:id="rId22" display="https://www.tme.eu/hr/en/details/zl201-40g/pin-headers/connfly/ds1021-1-40sf11-b/" xr:uid="{F7F3E930-C37E-49FD-94C5-C7F28DAE1FF1}"/>
-    <hyperlink ref="F21" r:id="rId23" xr:uid="{50E58A42-5E92-4204-8ABD-524325B56B67}"/>
-    <hyperlink ref="F17" r:id="rId24" xr:uid="{3E399706-9EC1-431B-AD19-FE5B90914E93}"/>
-    <hyperlink ref="F18" r:id="rId25" xr:uid="{6779E970-65B8-4206-B393-45EE96D5A7E8}"/>
-    <hyperlink ref="F3" r:id="rId26" xr:uid="{D321C547-CD58-4724-A04B-E0C6B8A12225}"/>
-    <hyperlink ref="F4" r:id="rId27" xr:uid="{6B737D48-67DC-4C5F-8B0D-F1E974D11A75}"/>
-    <hyperlink ref="F5" r:id="rId28" xr:uid="{E5FD6F18-5780-4884-A6D2-8762FBB8D19E}"/>
-    <hyperlink ref="F6" r:id="rId29" xr:uid="{F603AF18-9F04-4BE9-83FF-FCEBF50BE87C}"/>
-    <hyperlink ref="F11" r:id="rId30" xr:uid="{4313A3AA-304C-494B-8218-63F20BF91AC5}"/>
-    <hyperlink ref="F20" r:id="rId31" xr:uid="{753C3957-B785-4C2E-B432-67959234399B}"/>
-    <hyperlink ref="F19" r:id="rId32" xr:uid="{F3267F75-10C7-410D-BA21-80181D702A88}"/>
+    <hyperlink ref="J20" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="J19" r:id="rId15" xr:uid="{3EC0FADE-B5DB-495B-A25A-8E9C82905237}"/>
+    <hyperlink ref="F13" r:id="rId16" xr:uid="{0D186728-B786-4B2E-9671-D0877C50C69C}"/>
+    <hyperlink ref="F25" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="F24" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="F23" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="F17:F18" r:id="rId20" display="https://www.tme.eu/hr/en/details/zl201-40g/pin-headers/connfly/ds1021-1-40sf11-b/" xr:uid="{F7F3E930-C37E-49FD-94C5-C7F28DAE1FF1}"/>
+    <hyperlink ref="F17" r:id="rId21" xr:uid="{3E399706-9EC1-431B-AD19-FE5B90914E93}"/>
+    <hyperlink ref="F18" r:id="rId22" xr:uid="{6779E970-65B8-4206-B393-45EE96D5A7E8}"/>
+    <hyperlink ref="F3" r:id="rId23" xr:uid="{D321C547-CD58-4724-A04B-E0C6B8A12225}"/>
+    <hyperlink ref="F4" r:id="rId24" xr:uid="{6B737D48-67DC-4C5F-8B0D-F1E974D11A75}"/>
+    <hyperlink ref="F5" r:id="rId25" xr:uid="{E5FD6F18-5780-4884-A6D2-8762FBB8D19E}"/>
+    <hyperlink ref="F6" r:id="rId26" xr:uid="{F603AF18-9F04-4BE9-83FF-FCEBF50BE87C}"/>
+    <hyperlink ref="F11" r:id="rId27" xr:uid="{4313A3AA-304C-494B-8218-63F20BF91AC5}"/>
+    <hyperlink ref="F20" r:id="rId28" xr:uid="{753C3957-B785-4C2E-B432-67959234399B}"/>
+    <hyperlink ref="F19" r:id="rId29" xr:uid="{F3267F75-10C7-410D-BA21-80181D702A88}"/>
+    <hyperlink ref="F27" r:id="rId30" xr:uid="{B5B1F6F4-FF93-449C-8C9A-666CD7A198FA}"/>
+    <hyperlink ref="F28" r:id="rId31" xr:uid="{5B706843-ABC3-494A-8734-96F0C9FFF663}"/>
+    <hyperlink ref="F21" r:id="rId32" xr:uid="{8E8CE69B-19CD-452D-B1D2-1AE2F4321B46}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
